--- a/переводы-13.5/07 Die Sopranos.xlsx
+++ b/переводы-13.5/07 Die Sopranos.xlsx
@@ -6346,12 +6346,12 @@
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>das wollte ich nun wirklich nicht sagen</t>
+          <t>das will ich nun wirklich nicht sagen</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>я вовсе не это хотел сказать</t>
+          <t>я вовсе не это хочу сказать</t>
         </is>
       </c>
       <c r="H58" s="3" t="inlineStr">
@@ -6366,12 +6366,12 @@
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>Nein, das wollte ich nun wirklich nicht sagen – das Essen ist super!</t>
+          <t>Nein, das will ich nun wirklich nicht sagen – das Essen ist super!</t>
         </is>
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>Нет, я вовсе не это хотел сказать — еда супер!</t>
+          <t>Нет, я вовсе не это хочу сказать — еда супер!</t>
         </is>
       </c>
       <c r="L58" s="3" t="inlineStr">
@@ -6381,18 +6381,18 @@
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>No, that's not what I meant at all – the food is great! — Нет, я вовсе не это хотел сказать — еда супер! — Nein, das wollte ich nun wirklich nicht sagen – das Essen ist super!</t>
+          <t>No, that's not what I'm saying at all – the food is great! — Нет, я вовсе не это хочу сказать — еда супер! — Nein, das will ich nun wirklich nicht sagen – das Essen ist super!</t>
         </is>
       </c>
       <c r="N58" s="3" t="inlineStr">
         <is>
-          <t>Nein, das wollte ich nun wirklich nicht sagen – das Essen ist super! — Нет, я вовсе не это хотел сказать — еда супер!</t>
+          <t>Nein, das will ich nun wirklich nicht sagen – das Essen ist super! — Нет, я вовсе не это хочу сказать — еда супер!</t>
         </is>
       </c>
       <c r="O58" s="3" t="inlineStr"/>
       <c r="P58" s="3" t="inlineStr">
         <is>
-          <t>я ничего не хотел сказать / я правда хотел это сказать / я так и сказал</t>
+          <t>я ничего не хочу сказать / я правда хочу это сказать / я так и сказал</t>
         </is>
       </c>
       <c r="Q58" s="3" t="inlineStr">
@@ -10075,7 +10075,7 @@
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>das wollte ich nun wirklich nicht sagen</t>
+          <t>das will ich nun wirklich nicht sagen</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
@@ -10105,7 +10105,7 @@
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>nun wirklich nicht — сильное «вовсе не». wollte — Präteritum от wollen.</t>
+          <t>nun wirklich nicht — сильное «вовсе не». will — от wollen («хотеть»).</t>
         </is>
       </c>
     </row>
@@ -12588,7 +12588,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>Я тебе все твои сраные кости переломаю, сопляк!</t>
+          <t>Я тебе все твои сраные кости переломаю, засранец!</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
@@ -16032,7 +16032,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>Слушай сюда, больной ты дрочила!</t>
+          <t>Слушай сюда, урод больной!</t>
         </is>
       </c>
       <c r="H123" s="3" t="inlineStr">
@@ -16128,7 +16128,7 @@
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>sopranos-hasid-de|221.35</t>
+          <t>sopranos-hasid-de|221.23</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
@@ -16148,17 +16148,17 @@
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
-          <t>221.3</t>
+          <t>221.2</t>
         </is>
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>Leck mich doch.</t>
+          <t>Lass mich doch!</t>
         </is>
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>Да пошёл ты.</t>
+          <t>Да отстань ты!</t>
         </is>
       </c>
       <c r="H126" s="3" t="inlineStr">
@@ -16447,12 +16447,12 @@
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t>Wahrscheinlich nicht.</t>
+          <t>Wahrscheinlich...</t>
         </is>
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>Наверное, нет.</t>
+          <t>Наверное…</t>
         </is>
       </c>
       <c r="H133" s="3" t="inlineStr">
@@ -16741,12 +16741,12 @@
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>Nichts. In der Sache stimme ich dir zu, aber ich muss den Rat erteilen.</t>
+          <t>Nichts. In der Sache stimme ich dir zu, aber ich muss dir einen Rat erteilen.</t>
         </is>
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>Ничего. По сути я с тобой согласен, но должен дать совет.</t>
+          <t>Ничего. По сути я с тобой согласен, но должен дать тебе совет.</t>
         </is>
       </c>
       <c r="H140" s="3" t="inlineStr">
@@ -17077,12 +17077,12 @@
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>Phil, Phil, das wollte ich nun wirklich nicht sagen.</t>
+          <t>Phil, Phil, das will ich nun wirklich nicht sagen.</t>
         </is>
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>Фил, Фил, я вовсе не это хотел сказать.</t>
+          <t>Фил, Фил, я вовсе не это хочу сказать.</t>
         </is>
       </c>
       <c r="H148" s="3" t="inlineStr">
@@ -17502,7 +17502,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>Слушай сюда: в Джерси принимают любого долбаного придурка и сопляка.</t>
+          <t>Слушай сюда: в Джерси принимают любого долбаного придурка и засранца.</t>
         </is>
       </c>
       <c r="H158" s="3" t="inlineStr">
